--- a/data/trans_bre/P2C_R-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P2C_R-Provincia-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,31; 24,61</t>
+          <t>2,09; 23,39</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,47; 27,36</t>
+          <t>8,15; 28,01</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,18; 15,75</t>
+          <t>-5,69; 14,96</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,55; 3,6</t>
+          <t>-1,65; 3,87</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,27; 55,18</t>
+          <t>3,56; 50,65</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,44; 60,64</t>
+          <t>14,31; 62,41</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-10,35; 42,09</t>
+          <t>-10,78; 38,33</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-31,83; 158,67</t>
+          <t>-34,17; 169,24</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,49; 20,01</t>
+          <t>3,82; 19,45</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>10,08; 26,07</t>
+          <t>10,72; 25,87</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,07; 17,2</t>
+          <t>0,88; 18,13</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,87; 10,28</t>
+          <t>3,72; 10,6</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>13,54; 81,41</t>
+          <t>11,5; 79,64</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,39; 70,33</t>
+          <t>22,95; 70,53</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,29; 50,37</t>
+          <t>2,17; 52,96</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>33,2; 246,29</t>
+          <t>50,83; 255,51</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 18,68</t>
+          <t>-0,73; 18,57</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 16,54</t>
+          <t>-1,96; 16,82</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,93; 12,95</t>
+          <t>-5,31; 13,64</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 4,6</t>
+          <t>-1,87; 4,92</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 56,11</t>
+          <t>-1,87; 53,27</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-4,61; 35,57</t>
+          <t>-3,59; 36,69</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-10,93; 39,47</t>
+          <t>-11,88; 41,06</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-25,37; 119,2</t>
+          <t>-25,91; 135,49</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-6,68; 11,9</t>
+          <t>-6,57; 11,64</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,28; 22,59</t>
+          <t>6,01; 22,85</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,33; 24,12</t>
+          <t>4,86; 23,54</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-5,27; 6,4</t>
+          <t>-5,19; 6,23</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-12,95; 29,75</t>
+          <t>-12,62; 29,39</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,21; 52,72</t>
+          <t>11,6; 54,49</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,92; 87,09</t>
+          <t>11,5; 80,31</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-45,76; 105,57</t>
+          <t>-39,31; 106,56</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,52; 18,28</t>
+          <t>-5,23; 18,67</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,98; 29,7</t>
+          <t>5,05; 28,89</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-9,33; 13,34</t>
+          <t>-9,7; 13,41</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-8,18; 0,72</t>
+          <t>-8,13; 0,94</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-16,39; 75,47</t>
+          <t>-14,78; 89,19</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,88; 91,77</t>
+          <t>11,58; 88,47</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-14,12; 26,01</t>
+          <t>-15,03; 24,76</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-73,23; 10,78</t>
+          <t>-73,31; 16,72</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-13,42; 7,33</t>
+          <t>-12,83; 7,79</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-2,29; 18,47</t>
+          <t>-2,2; 19,91</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-8,79; 12,2</t>
+          <t>-9,67; 11,31</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-4,07; 5,84</t>
+          <t>-4,26; 5,79</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-28,15; 19,35</t>
+          <t>-27,43; 20,96</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-4,47; 41,51</t>
+          <t>-4,0; 45,14</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-19,25; 34,11</t>
+          <t>-21,35; 32,73</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-28,81; 68,33</t>
+          <t>-30,92; 66,12</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>10,46; 24,65</t>
+          <t>9,7; 23,23</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,68; 10,66</t>
+          <t>-3,45; 9,77</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,67; 14,8</t>
+          <t>0,49; 15,37</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,53; 56,19</t>
+          <t>0,5; 60,08</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>26,57; 78,64</t>
+          <t>25,3; 76,49</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-5,69; 17,88</t>
+          <t>-5,26; 16,83</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,23; 39,2</t>
+          <t>1,01; 40,76</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>13,37; 4288,91</t>
+          <t>13,55; 2915,87</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,05; 13,87</t>
+          <t>2,41; 13,96</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>8,41; 20,81</t>
+          <t>8,71; 21,27</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,46; 12,99</t>
+          <t>0,77; 13,53</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8,01; 22,09</t>
+          <t>7,69; 22,84</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>6,07; 46,52</t>
+          <t>6,55; 45,84</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,74; 48,17</t>
+          <t>17,72; 49,57</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,95; 26,73</t>
+          <t>1,14; 27,83</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>42,21; 358,6</t>
+          <t>43,04; 396,86</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>5,88; 12,05</t>
+          <t>6,22; 12,09</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>9,28; 15,37</t>
+          <t>9,38; 15,15</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3,95; 10,4</t>
+          <t>4,22; 10,23</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3,41; 24,67</t>
+          <t>3,52; 24,39</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>14,98; 34,01</t>
+          <t>16,08; 34,0</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>18,16; 32,31</t>
+          <t>18,43; 31,87</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>8,82; 24,6</t>
+          <t>9,23; 24,11</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>42,17; 321,31</t>
+          <t>43,21; 380,66</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2C_R-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P2C_R-Provincia-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,15</t>
+          <t>2,13</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>31,27%</t>
+          <t>61,77%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,09; 23,39</t>
+          <t>1,47; 24,74</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8,15; 28,01</t>
+          <t>6,75; 27,51</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,69; 14,96</t>
+          <t>-4,81; 16,43</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 3,87</t>
+          <t>-0,79; 4,6</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,56; 50,65</t>
+          <t>2,6; 54,87</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,31; 62,41</t>
+          <t>11,89; 62,8</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-10,78; 38,33</t>
+          <t>-9,93; 42,46</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-34,17; 169,24</t>
+          <t>-20,62; 209,59</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6,87</t>
+          <t>6,44</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>124,24%</t>
+          <t>98,38%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,82; 19,45</t>
+          <t>3,76; 19,23</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>10,72; 25,87</t>
+          <t>10,41; 25,62</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,88; 18,13</t>
+          <t>0,96; 17,53</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,72; 10,6</t>
+          <t>2,88; 10,15</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>11,5; 79,64</t>
+          <t>11,47; 80,24</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,95; 70,53</t>
+          <t>22,26; 67,54</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,17; 52,96</t>
+          <t>2,46; 51,93</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>50,83; 255,51</t>
+          <t>31,36; 207,01</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,49</t>
+          <t>1,01</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>27,54%</t>
+          <t>17,68%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 18,57</t>
+          <t>0,01; 19,2</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,96; 16,82</t>
+          <t>-3,32; 15,87</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,31; 13,64</t>
+          <t>-5,95; 13,25</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 4,92</t>
+          <t>-2,31; 4,22</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 53,27</t>
+          <t>0,12; 55,94</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-3,59; 36,69</t>
+          <t>-6,04; 34,09</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-11,88; 41,06</t>
+          <t>-13,26; 39,47</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-25,91; 135,49</t>
+          <t>-31,6; 104,64</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1,42</t>
+          <t>4,08</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>44,7%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-6,57; 11,64</t>
+          <t>-6,7; 13,17</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,01; 22,85</t>
+          <t>5,28; 22,59</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,86; 23,54</t>
+          <t>4,49; 23,66</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-5,19; 6,23</t>
+          <t>-1,5; 8,69</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-12,62; 29,39</t>
+          <t>-12,99; 31,66</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,6; 54,49</t>
+          <t>10,46; 52,71</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11,5; 80,31</t>
+          <t>10,96; 83,15</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-39,31; 106,56</t>
+          <t>-13,1; 144,9</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-3,36</t>
+          <t>-2,37</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-41,3%</t>
+          <t>-26,71%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,23; 18,67</t>
+          <t>-6,09; 17,7</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,05; 28,89</t>
+          <t>7,64; 30,43</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-9,7; 13,41</t>
+          <t>-10,0; 13,77</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-8,13; 0,94</t>
+          <t>-7,25; 1,75</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-14,78; 89,19</t>
+          <t>-17,34; 78,65</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,58; 88,47</t>
+          <t>16,54; 95,58</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-15,03; 24,76</t>
+          <t>-15,13; 26,47</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-73,31; 16,72</t>
+          <t>-60,14; 29,06</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1,0</t>
+          <t>0,75</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>6,48%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-12,83; 7,79</t>
+          <t>-13,72; 7,6</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 19,91</t>
+          <t>-1,89; 18,37</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-9,67; 11,31</t>
+          <t>-9,96; 11,68</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-4,26; 5,79</t>
+          <t>-4,48; 4,9</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-27,43; 20,96</t>
+          <t>-27,58; 19,95</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-4,0; 45,14</t>
+          <t>-3,4; 40,99</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-21,35; 32,73</t>
+          <t>-22,32; 33,42</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-30,92; 66,12</t>
+          <t>-31,69; 51,06</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>24,28</t>
+          <t>1,71</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>798,26%</t>
+          <t>53,09%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>9,7; 23,23</t>
+          <t>10,08; 23,72</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,45; 9,77</t>
+          <t>-3,26; 10,11</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,49; 15,37</t>
+          <t>0,73; 15,43</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,5; 60,08</t>
+          <t>-0,43; 3,75</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>25,3; 76,49</t>
+          <t>26,52; 77,85</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-5,26; 16,83</t>
+          <t>-5,08; 17,72</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,01; 40,76</t>
+          <t>1,69; 42,92</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>13,55; 2915,87</t>
+          <t>-12,11; 162,45</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>13,84</t>
+          <t>9,42</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>107,32%</t>
+          <t>52,71%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,41; 13,96</t>
+          <t>1,78; 13,68</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>8,71; 21,27</t>
+          <t>8,91; 21,27</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,77; 13,53</t>
+          <t>0,31; 13,29</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7,69; 22,84</t>
+          <t>5,38; 13,33</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>6,55; 45,84</t>
+          <t>5,36; 45,09</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>17,72; 49,57</t>
+          <t>18,2; 50,27</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,14; 27,83</t>
+          <t>0,53; 26,94</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>43,04; 396,86</t>
+          <t>26,43; 83,53</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>8,89</t>
+          <t>4,0</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>115,02%</t>
+          <t>45,06%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>6,22; 12,09</t>
+          <t>6,13; 12,35</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>9,38; 15,15</t>
+          <t>9,08; 15,09</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4,22; 10,23</t>
+          <t>3,69; 10,01</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3,52; 24,39</t>
+          <t>2,48; 5,5</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>16,08; 34,0</t>
+          <t>15,62; 34,79</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>18,43; 31,87</t>
+          <t>17,68; 31,63</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>9,23; 24,11</t>
+          <t>8,0; 23,76</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>43,21; 380,66</t>
+          <t>26,03; 68,66</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2C_R-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P2C_R-Provincia-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con al menos un miembro que requiere cuidados habituales por la persona entrevistada</t>
+          <t>Población que convive con al menos un miembro que requiere cuidados habituales por la persona entrevistada</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
